--- a/rules/CORE-000370/negative/01/data/unit-test-coreid-CG0143-negative.xlsx
+++ b/rules/CORE-000370/negative/01/data/unit-test-coreid-CG0143-negative.xlsx
@@ -44,7 +44,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +94,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,224 +621,224 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>ds.xpt</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>DSTERM</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>INFORMED CONSENT FOR STUDY OBTAINED</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ds.xpt</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>DSSTDTC</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2018-03-06</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ds.xpt</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>$min_ds_dsstdtc</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2018-03-06</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>dm.xpt</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>RFICDTC</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2018-05-20</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ds.xpt</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="n">
         <v>22</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>DSTERM</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>INFORMED CONSENT OBTAINED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ds.xpt</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>22</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>DSSTDTC</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2018-04-06</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ds.xpt</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" t="n">
         <v>22</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>$min_ds_dsstdtc</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2018-04-06</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>dm.xpt</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>RFICDTC</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2019-08-15</t>
         </is>
@@ -840,26 +846,210 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DSTERM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>INFORMED CONSENT FOR STUDY OBTAINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>33</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DSSTDTC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>$min_ds_dsstdtc</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>dm.xpt</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>RFICDTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>34</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DSTERM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>INFORMED CONSENT FOR STUDY OBTAINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>34</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DSSTDTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>34</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>$min_ds_dsstdtc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RFICDTC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
         </is>
       </c>
     </row>
@@ -874,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,6 +2209,7 @@
           <t>2019-02-19T10:55</t>
         </is>
       </c>
+      <c r="I10" s="7" t="n"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2021-02-18</t>
@@ -2088,6 +2279,126 @@
         </is>
       </c>
       <c r="AA10" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDISCCORE01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GUARD-DSST-NULL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>076000300003</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2018-04-02T11:32</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2019-02-19T10:55</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2018-04-02T11:32</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2019-02-19T10:55</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2022-02-20</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0760003</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1940-01-14</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>YEARS</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>IKD</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>IKd</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>IKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>IKd</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>BRA</t>
         </is>
@@ -2104,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3586,7 +3897,7 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>INFORMED CONSENT FOR STUDY OBTAINED</t>
         </is>
@@ -3601,11 +3912,47 @@
           <t>PROTOCOL MILESTONE</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CDISCCORE01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GUARD-DSST-NULL</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>INFORMED CONSENT FOR STUDY OBTAINED</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>INFORMED CONSENT OBTAINED</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PROTOCOL MILESTONE</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/CORE-000370/negative/01/data/unit-test-coreid-CG0143-negative.xlsx
+++ b/rules/CORE-000370/negative/01/data/unit-test-coreid-CG0143-negative.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -95,6 +95,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1051,118 @@
       <c r="F17" t="inlineStr">
         <is>
           <t>2018-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DSTERM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>INFORMED CONSENT FOR STUDY OBTAINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DSSTDTC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2018-02-01T09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ds.xpt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>$min_ds_dsstdtc</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2018-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RFICDTC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2018-02-10</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2399,6 +2512,126 @@
         </is>
       </c>
       <c r="AA11" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CDISCCORE01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GUARD-DSST-TIME</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>076000300003</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2018-04-02T11:32</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2019-02-19T10:55</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2018-04-02T11:32</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2019-02-19T10:55</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>2018-02-10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2022-02-20</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0760003</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1940-01-14</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>YEARS</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>IKD</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>IKd</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>IKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>IKd</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>BRA</t>
         </is>
@@ -2415,7 +2648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3954,6 +4187,46 @@
       </c>
       <c r="J34" s="7" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CDISCCORE01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GUARD-DSST-TIME</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>INFORMED CONSENT FOR STUDY OBTAINED</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>INFORMED CONSENT OBTAINED</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PROTOCOL MILESTONE</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>2018-02-01T09:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
